--- a/CUQ/_docs/quantities.xlsx
+++ b/CUQ/_docs/quantities.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gregordudle/Developments/Semantic-SI/CUQ/_docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gruber04\git_repos\BIPM\Semantic-SI\CUQ\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5349FF1-B485-9C46-BD6A-9CBE7A96AC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4868367-1E6F-4CDB-B296-2DC674DB2BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{7BF4A3DD-9852-8D48-87BE-97C5CDB01446}"/>
+    <workbookView xWindow="28680" yWindow="-8310" windowWidth="38640" windowHeight="21390" xr2:uid="{7BF4A3DD-9852-8D48-87BE-97C5CDB01446}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -680,9 +680,6 @@
     <t>induction magnétique</t>
   </si>
   <si>
-    <t>degré Celsius</t>
-  </si>
-  <si>
     <t>flux lumineux</t>
   </si>
   <si>
@@ -692,9 +689,6 @@
     <t>activité d'un radionucléide</t>
   </si>
   <si>
-    <t>dose absorbé, kerma</t>
-  </si>
-  <si>
     <t>équivalent de dose</t>
   </si>
   <si>
@@ -813,6 +807,30 @@
   </si>
   <si>
     <t>entropie molaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">débit de dose absorbée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">intensité énergétique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">luminance énergétique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">concentration de l’activité catalytique </t>
+  </si>
+  <si>
+    <t>degreeCelsius</t>
+  </si>
+  <si>
+    <t>meters2</t>
+  </si>
+  <si>
+    <t>Température Celsius</t>
+  </si>
+  <si>
+    <t>dose absorbée, kerma</t>
   </si>
   <si>
     <r>
@@ -821,7 +839,6 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color theme="1"/>
         <rFont val="SymbolMT"/>
       </rPr>
       <t>γ</t>
@@ -829,29 +846,10 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color theme="1"/>
         <rFont val="TimesNewRomanPSMT"/>
       </rPr>
       <t xml:space="preserve">) </t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">débit de dose absorbée </t>
-  </si>
-  <si>
-    <t xml:space="preserve">intensité énergétique </t>
-  </si>
-  <si>
-    <t xml:space="preserve">luminance énergétique </t>
-  </si>
-  <si>
-    <t xml:space="preserve">concentration de l’activité catalytique </t>
-  </si>
-  <si>
-    <t>degreeCelsius</t>
-  </si>
-  <si>
-    <t>meters2</t>
   </si>
 </sst>
 </file>
@@ -867,22 +865,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="12"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="TimesNewRomanPSMT"/>
+      <name val="SymbolMT"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="SymbolMT"/>
+      <name val="TimesNewRomanPSMT"/>
     </font>
   </fonts>
   <fills count="2">
@@ -902,17 +896,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -928,7 +920,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1224,954 +1216,955 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6531254D-9659-F841-A972-54E4401B1931}">
-  <dimension ref="A1:I67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:F67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="7" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11" style="1"/>
+    <col min="2" max="3" width="30.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.875" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D6" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D7" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="D8" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>196</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>202</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>203</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D31" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F12" t="s">
-        <v>100</v>
-      </c>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>204</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>183</v>
-      </c>
-      <c r="F13" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" t="s">
-        <v>205</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>206</v>
-      </c>
-      <c r="D15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s">
-        <v>208</v>
-      </c>
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>209</v>
-      </c>
-      <c r="D18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>210</v>
-      </c>
-      <c r="D19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>211</v>
-      </c>
-      <c r="D20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>212</v>
-      </c>
-      <c r="D21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" t="s">
-        <v>214</v>
-      </c>
-      <c r="D24" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" t="s">
-        <v>215</v>
-      </c>
-      <c r="D25" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" t="s">
-        <v>177</v>
-      </c>
-      <c r="F25" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" t="s">
-        <v>216</v>
-      </c>
-      <c r="D26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" t="s">
-        <v>217</v>
-      </c>
-      <c r="D27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" t="s">
-        <v>218</v>
-      </c>
-      <c r="D28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="s">
-        <v>219</v>
-      </c>
-      <c r="D29" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
-        <v>165</v>
-      </c>
-      <c r="B30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" t="s">
-        <v>220</v>
-      </c>
-      <c r="D30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="E33" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E34" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" t="s">
-        <v>91</v>
-      </c>
-      <c r="E32" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" t="s">
-        <v>229</v>
-      </c>
-      <c r="E33" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>230</v>
-      </c>
-      <c r="E34" t="s">
-        <v>96</v>
-      </c>
-      <c r="F34" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
-        <v>101</v>
-      </c>
-      <c r="B35" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
-        <v>103</v>
-      </c>
-      <c r="B36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" t="s">
-        <v>232</v>
-      </c>
-      <c r="E36" t="s">
-        <v>195</v>
-      </c>
-      <c r="F36" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
-        <v>105</v>
-      </c>
-      <c r="B37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" t="s">
-        <v>233</v>
-      </c>
-      <c r="E37" t="s">
-        <v>178</v>
-      </c>
-      <c r="F37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" t="s">
-        <v>234</v>
-      </c>
-      <c r="E38" t="s">
-        <v>173</v>
-      </c>
-      <c r="F38" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" t="s">
-        <v>110</v>
-      </c>
-      <c r="B39" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" t="s">
-        <v>235</v>
-      </c>
-      <c r="E39" t="s">
-        <v>179</v>
-      </c>
-      <c r="F39" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
-        <v>112</v>
-      </c>
-      <c r="B40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
-        <v>114</v>
-      </c>
-      <c r="B41" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
-        <v>116</v>
-      </c>
-      <c r="B42" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" t="s">
-        <v>118</v>
-      </c>
-      <c r="B43" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
-        <v>120</v>
-      </c>
-      <c r="B44" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
-        <v>122</v>
-      </c>
-      <c r="B45" t="s">
-        <v>121</v>
-      </c>
-      <c r="C45" t="s">
-        <v>241</v>
-      </c>
-      <c r="E45" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" t="s">
-        <v>124</v>
-      </c>
-      <c r="B46" t="s">
-        <v>123</v>
-      </c>
-      <c r="C46" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
-        <v>125</v>
-      </c>
-      <c r="B47" t="s">
-        <v>126</v>
-      </c>
-      <c r="C47" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" t="s">
-        <v>127</v>
-      </c>
-      <c r="B48" t="s">
-        <v>128</v>
-      </c>
-      <c r="C48" t="s">
-        <v>244</v>
-      </c>
-      <c r="E48" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" t="s">
-        <v>129</v>
-      </c>
-      <c r="B49" t="s">
-        <v>130</v>
-      </c>
-      <c r="C49" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" t="s">
-        <v>131</v>
-      </c>
-      <c r="B50" t="s">
-        <v>132</v>
-      </c>
-      <c r="C50" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" t="s">
-        <v>133</v>
-      </c>
-      <c r="B51" t="s">
-        <v>134</v>
-      </c>
-      <c r="C51" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" t="s">
-        <v>135</v>
-      </c>
-      <c r="B52" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" t="s">
-        <v>248</v>
-      </c>
-      <c r="E52" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" t="s">
-        <v>137</v>
-      </c>
-      <c r="B53" t="s">
-        <v>138</v>
-      </c>
-      <c r="C53" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" t="s">
-        <v>139</v>
-      </c>
-      <c r="B54" t="s">
-        <v>140</v>
-      </c>
-      <c r="C54" t="s">
-        <v>250</v>
-      </c>
-      <c r="E54" t="s">
-        <v>192</v>
-      </c>
-      <c r="F54" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" t="s">
-        <v>141</v>
-      </c>
-      <c r="B55" t="s">
-        <v>142</v>
-      </c>
-      <c r="C55" t="s">
-        <v>251</v>
-      </c>
-      <c r="E55" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" t="s">
-        <v>143</v>
-      </c>
-      <c r="B56" t="s">
-        <v>144</v>
-      </c>
-      <c r="C56" t="s">
-        <v>252</v>
-      </c>
-      <c r="E56" t="s">
-        <v>182</v>
-      </c>
-      <c r="F56" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" t="s">
-        <v>145</v>
-      </c>
-      <c r="B57" t="s">
-        <v>146</v>
-      </c>
-      <c r="C57" t="s">
-        <v>253</v>
-      </c>
-      <c r="E57" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" t="s">
-        <v>147</v>
-      </c>
-      <c r="B58" t="s">
-        <v>148</v>
-      </c>
-      <c r="C58" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" t="s">
-        <v>149</v>
-      </c>
-      <c r="B59" t="s">
-        <v>150</v>
-      </c>
-      <c r="C59" t="s">
-        <v>255</v>
-      </c>
-      <c r="E59" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" t="s">
-        <v>151</v>
-      </c>
-      <c r="B60" t="s">
-        <v>152</v>
-      </c>
-      <c r="C60" t="s">
-        <v>256</v>
-      </c>
-      <c r="E60" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" t="s">
-        <v>155</v>
-      </c>
-      <c r="B61" t="s">
-        <v>154</v>
-      </c>
-      <c r="C61" t="s">
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E61" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" t="s">
-        <v>153</v>
-      </c>
-      <c r="B62" t="s">
-        <v>156</v>
-      </c>
-      <c r="C62" t="s">
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
-      <c r="A63" t="s">
-        <v>157</v>
-      </c>
-      <c r="B63" t="s">
-        <v>158</v>
-      </c>
-      <c r="C63" t="s">
+    <row r="66" spans="1:6">
+      <c r="A66" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
-      <c r="A64" t="s">
-        <v>159</v>
-      </c>
-      <c r="B64" t="s">
-        <v>160</v>
-      </c>
-      <c r="C64" t="s">
+    <row r="67" spans="1:6">
+      <c r="A67" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
-        <v>161</v>
-      </c>
-      <c r="B65" t="s">
-        <v>162</v>
-      </c>
-      <c r="C65" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
-        <v>163</v>
-      </c>
-      <c r="B66" t="s">
-        <v>164</v>
-      </c>
-      <c r="C66" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
-        <v>166</v>
-      </c>
-      <c r="B67" t="s">
-        <v>167</v>
-      </c>
-      <c r="C67" t="s">
-        <v>263</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="E67" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" s="1" t="s">
         <v>168</v>
       </c>
     </row>

--- a/CUQ/_docs/quantities.xlsx
+++ b/CUQ/_docs/quantities.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gruber04\git_repos\BIPM\Semantic-SI\CUQ\_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/n00002621/PycharmProjects/SI-Reference-Point-2023/CUQ/_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4868367-1E6F-4CDB-B296-2DC674DB2BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826C121A-DC50-D545-B190-B891360648F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-8310" windowWidth="38640" windowHeight="21390" xr2:uid="{7BF4A3DD-9852-8D48-87BE-97C5CDB01446}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="21580" xr2:uid="{7BF4A3DD-9852-8D48-87BE-97C5CDB01446}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="267">
   <si>
     <t>velocity</t>
   </si>
@@ -221,9 +221,6 @@
     <t>ABDO</t>
   </si>
   <si>
-    <t>absorbed dose</t>
-  </si>
-  <si>
     <t>gray</t>
   </si>
   <si>
@@ -305,18 +302,12 @@
     <t>area</t>
   </si>
   <si>
-    <t>LENG+2</t>
-  </si>
-  <si>
     <t>VOLU</t>
   </si>
   <si>
     <t>volume</t>
   </si>
   <si>
-    <t>LENG+3</t>
-  </si>
-  <si>
     <t>VELO</t>
   </si>
   <si>
@@ -689,6 +680,9 @@
     <t>activité d'un radionucléide</t>
   </si>
   <si>
+    <t>dose absorbé, kerma</t>
+  </si>
+  <si>
     <t>équivalent de dose</t>
   </si>
   <si>
@@ -807,30 +801,6 @@
   </si>
   <si>
     <t>entropie molaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">débit de dose absorbée </t>
-  </si>
-  <si>
-    <t xml:space="preserve">intensité énergétique </t>
-  </si>
-  <si>
-    <t xml:space="preserve">luminance énergétique </t>
-  </si>
-  <si>
-    <t xml:space="preserve">concentration de l’activité catalytique </t>
-  </si>
-  <si>
-    <t>degreeCelsius</t>
-  </si>
-  <si>
-    <t>meters2</t>
-  </si>
-  <si>
-    <t>Température Celsius</t>
-  </si>
-  <si>
-    <t>dose absorbée, kerma</t>
   </si>
   <si>
     <r>
@@ -839,6 +809,7 @@
     <r>
       <rPr>
         <sz val="9"/>
+        <color theme="1"/>
         <rFont val="SymbolMT"/>
       </rPr>
       <t>γ</t>
@@ -846,10 +817,44 @@
     <r>
       <rPr>
         <sz val="9"/>
+        <color theme="1"/>
         <rFont val="TimesNewRomanPSMT"/>
       </rPr>
       <t xml:space="preserve">) </t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">débit de dose absorbée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">intensité énergétique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">luminance énergétique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">concentration de l’activité catalytique </t>
+  </si>
+  <si>
+    <t>degreeCelsius</t>
+  </si>
+  <si>
+    <t>meters2</t>
+  </si>
+  <si>
+    <t>meters3</t>
+  </si>
+  <si>
+    <t>LENG2</t>
+  </si>
+  <si>
+    <t>LENG3</t>
+  </si>
+  <si>
+    <t>absorbed dose, kerma</t>
+  </si>
+  <si>
+    <t>Température Celsius</t>
   </si>
 </sst>
 </file>
@@ -865,18 +870,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="SymbolMT"/>
+      <color theme="1"/>
+      <name val="TimesNewRomanPSMT"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="TimesNewRomanPSMT"/>
+      <color theme="1"/>
+      <name val="SymbolMT"/>
     </font>
   </fonts>
   <fills count="2">
@@ -896,15 +905,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -920,7 +931,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1216,956 +1227,958 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6531254D-9659-F841-A972-54E4401B1931}">
-  <dimension ref="A1:F67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="11" style="1"/>
-    <col min="2" max="3" width="30.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="17.625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="11" style="1"/>
+    <col min="2" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="7" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>197</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
         <v>198</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>223</v>
+      </c>
+      <c r="F12" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>180</v>
+      </c>
+      <c r="F13" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>205</v>
+      </c>
+      <c r="D17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>206</v>
+      </c>
+      <c r="D18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>207</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>209</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>210</v>
+      </c>
+      <c r="D22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>266</v>
+      </c>
+      <c r="D24" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" t="s">
+        <v>211</v>
+      </c>
+      <c r="D25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
+        <v>212</v>
+      </c>
+      <c r="D26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>213</v>
+      </c>
+      <c r="D27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C28" t="s">
+        <v>214</v>
+      </c>
+      <c r="D28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
+        <v>215</v>
+      </c>
+      <c r="D29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" t="s">
+        <v>216</v>
+      </c>
+      <c r="D30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" t="s">
+        <v>224</v>
+      </c>
+      <c r="D31" t="s">
+        <v>261</v>
+      </c>
+      <c r="E31" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" t="s">
+        <v>262</v>
+      </c>
+      <c r="E32" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>225</v>
+      </c>
+      <c r="E33" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>226</v>
+      </c>
+      <c r="E34" t="s">
+        <v>93</v>
+      </c>
+      <c r="F34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="B35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="B36" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" t="s">
+        <v>228</v>
+      </c>
+      <c r="E36" t="s">
+        <v>192</v>
+      </c>
+      <c r="F36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" t="s">
+        <v>229</v>
+      </c>
+      <c r="E37" t="s">
+        <v>175</v>
+      </c>
+      <c r="F37" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" t="s">
+        <v>230</v>
+      </c>
+      <c r="E38" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" t="s">
+        <v>231</v>
+      </c>
+      <c r="E39" t="s">
+        <v>176</v>
+      </c>
+      <c r="F39" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>117</v>
+      </c>
+      <c r="B44" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>119</v>
+      </c>
+      <c r="B45" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45" t="s">
+        <v>237</v>
+      </c>
+      <c r="E45" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>122</v>
+      </c>
+      <c r="B47" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" t="s">
+        <v>240</v>
+      </c>
+      <c r="E48" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" t="s">
+        <v>127</v>
+      </c>
+      <c r="C49" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>130</v>
+      </c>
+      <c r="B51" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>132</v>
+      </c>
+      <c r="B52" t="s">
+        <v>133</v>
+      </c>
+      <c r="C52" t="s">
+        <v>244</v>
+      </c>
+      <c r="E52" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>134</v>
+      </c>
+      <c r="B53" t="s">
+        <v>135</v>
+      </c>
+      <c r="C53" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" t="s">
+        <v>137</v>
+      </c>
+      <c r="C54" t="s">
+        <v>246</v>
+      </c>
+      <c r="E54" t="s">
+        <v>189</v>
+      </c>
+      <c r="F54" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>138</v>
+      </c>
+      <c r="B55" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" t="s">
+        <v>247</v>
+      </c>
+      <c r="E55" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="1" t="s">
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" t="s">
+        <v>141</v>
+      </c>
+      <c r="C56" t="s">
+        <v>248</v>
+      </c>
+      <c r="E56" t="s">
+        <v>179</v>
+      </c>
+      <c r="F56" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>142</v>
+      </c>
+      <c r="B57" t="s">
+        <v>143</v>
+      </c>
+      <c r="C57" t="s">
+        <v>249</v>
+      </c>
+      <c r="E57" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>144</v>
+      </c>
+      <c r="B58" t="s">
+        <v>145</v>
+      </c>
+      <c r="C58" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+      <c r="B59" t="s">
+        <v>147</v>
+      </c>
+      <c r="C59" t="s">
+        <v>251</v>
+      </c>
+      <c r="E59" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="1" t="s">
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C60" t="s">
+        <v>252</v>
+      </c>
+      <c r="E60" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="1" t="s">
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>152</v>
+      </c>
+      <c r="B61" t="s">
+        <v>151</v>
+      </c>
+      <c r="C61" t="s">
+        <v>253</v>
+      </c>
+      <c r="E61" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>150</v>
+      </c>
+      <c r="B62" t="s">
+        <v>153</v>
+      </c>
+      <c r="C62" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
+        <v>154</v>
+      </c>
+      <c r="B63" t="s">
+        <v>155</v>
+      </c>
+      <c r="C63" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
+        <v>156</v>
+      </c>
+      <c r="B64" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
+        <v>158</v>
+      </c>
+      <c r="B65" t="s">
+        <v>159</v>
+      </c>
+      <c r="C65" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
+        <v>160</v>
+      </c>
+      <c r="B66" t="s">
+        <v>161</v>
+      </c>
+      <c r="C66" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
+        <v>163</v>
+      </c>
+      <c r="B67" t="s">
+        <v>164</v>
+      </c>
+      <c r="C67" t="s">
+        <v>259</v>
+      </c>
+      <c r="E67" t="s">
+        <v>187</v>
+      </c>
+      <c r="F67" t="s">
         <v>165</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
   </sheetData>
